--- a/data/trans_bre/IP11A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP11A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,97</t>
+          <t>23,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 78,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,21</t>
+          <t>0,0; 76,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-33,48</t>
+          <t>-32,75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 0,0</t>
+          <t>-52,42; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,14</t>
+          <t>0,0; 53,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-81,09; 0,0</t>
+          <t>-81,26; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,45</t>
+          <t>33,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 0,0</t>
+          <t>-22,72; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 79,06</t>
+          <t>-36,44; 61,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 0,0</t>
+          <t>-42,24; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 0,0</t>
+          <t>-34,63; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -1,05</t>
+          <t>-10,17; -1,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,85</t>
+          <t>-7,83; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 22,24</t>
+          <t>-0,95; 23,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 16,62</t>
+          <t>-12,68; 14,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
